--- a/Results/04_UVC_CPD_percentage_pvals_location.xlsx
+++ b/Results/04_UVC_CPD_percentage_pvals_location.xlsx
@@ -93,22 +93,22 @@
     <t>30 J/m²</t>
   </si>
   <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>300 J/m²</t>
+  </si>
+  <si>
+    <t>1000 J/m²</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>2000 J/m²</t>
+  </si>
+  <si>
     <t>***</t>
-  </si>
-  <si>
-    <t>**</t>
-  </si>
-  <si>
-    <t>300 J/m²</t>
-  </si>
-  <si>
-    <t>1000 J/m²</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>2000 J/m²</t>
   </si>
 </sst>
 </file>
@@ -161,49 +161,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>104790</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>47632</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Grafik 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1524000" y="3238500"/>
-          <a:ext cx="104790" cy="47632"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -564,7 +521,7 @@
         <v>19</v>
       </c>
       <c r="L2">
-        <v>0.74729729729729699</v>
+        <v>0.75764705882352901</v>
       </c>
       <c r="M2" t="s">
         <v>20</v>
@@ -605,7 +562,7 @@
         <v>19</v>
       </c>
       <c r="L3">
-        <v>0.47639393939393898</v>
+        <v>0.488213333333333</v>
       </c>
       <c r="M3" t="s">
         <v>20</v>
@@ -637,19 +594,19 @@
         <v>11</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J4">
-        <v>3.0299999999999999E-4</v>
+        <v>8.8300000000000003E-2</v>
       </c>
       <c r="K4" t="s">
         <v>19</v>
       </c>
       <c r="L4">
-        <v>9.5748000000000003E-4</v>
+        <v>0.14770181818181799</v>
       </c>
       <c r="M4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -678,19 +635,19 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J5">
-        <v>7.4700000000000005E-4</v>
+        <v>3.3500000000000002E-2</v>
       </c>
       <c r="K5" t="s">
         <v>19</v>
       </c>
       <c r="L5">
-        <v>1.9670999999999998E-3</v>
+        <v>6.8488888888888905E-2</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -698,7 +655,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -719,19 +676,19 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>16.5</v>
+        <v>45</v>
       </c>
       <c r="J6">
-        <v>8.9999999999999998E-4</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="K6" t="s">
         <v>19</v>
       </c>
       <c r="L6">
-        <v>2.2048181818181802E-3</v>
+        <v>0.38933333333333298</v>
       </c>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -739,7 +696,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
@@ -760,19 +717,19 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J7">
-        <v>7.4200000000000004E-4</v>
+        <v>1.7100000000000001E-2</v>
       </c>
       <c r="K7" t="s">
         <v>19</v>
       </c>
       <c r="L7">
-        <v>1.9670999999999998E-3</v>
+        <v>3.9043902439024399E-2</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -780,7 +737,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -801,16 +758,16 @@
         <v>11</v>
       </c>
       <c r="I8">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="J8">
-        <v>9.0500000000000004E-5</v>
+        <v>5.1599999999999997E-3</v>
       </c>
       <c r="K8" t="s">
         <v>19</v>
       </c>
       <c r="L8">
-        <v>4.8979999999999998E-4</v>
+        <v>1.6369655172413799E-2</v>
       </c>
       <c r="M8" t="s">
         <v>24</v>
@@ -821,7 +778,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -842,19 +799,19 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>6.3899999999999995E-5</v>
+        <v>2.02E-4</v>
       </c>
       <c r="K9" t="s">
         <v>19</v>
       </c>
       <c r="L9">
-        <v>4.8979999999999998E-4</v>
+        <v>1.03244444444444E-3</v>
       </c>
       <c r="M9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -862,7 +819,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -883,19 +840,19 @@
         <v>11</v>
       </c>
       <c r="I10">
-        <v>5.5</v>
+        <v>32.5</v>
       </c>
       <c r="J10">
-        <v>9.2499999999999999E-5</v>
+        <v>6.6100000000000006E-2</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
       </c>
       <c r="L10">
-        <v>4.8979999999999998E-4</v>
+        <v>0.11694615384615401</v>
       </c>
       <c r="M10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -903,7 +860,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
@@ -924,19 +881,19 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>6.3399999999999996E-5</v>
+        <v>1.75E-3</v>
       </c>
       <c r="K11" t="s">
         <v>19</v>
       </c>
       <c r="L11">
-        <v>4.8979999999999998E-4</v>
+        <v>6.70833333333333E-3</v>
       </c>
       <c r="M11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -974,7 +931,7 @@
         <v>19</v>
       </c>
       <c r="L12">
-        <v>0.74729729729729699</v>
+        <v>0.75764705882352901</v>
       </c>
       <c r="M12" t="s">
         <v>20</v>
@@ -1015,7 +972,7 @@
         <v>19</v>
       </c>
       <c r="L13">
-        <v>0.47639393939393898</v>
+        <v>0.488213333333333</v>
       </c>
       <c r="M13" t="s">
         <v>20</v>
@@ -1056,10 +1013,10 @@
         <v>19</v>
       </c>
       <c r="L14">
-        <v>6.1027499999999997E-3</v>
+        <v>1.09338461538462E-2</v>
       </c>
       <c r="M14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -1088,19 +1045,19 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J15">
-        <v>1.91E-3</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="K15" t="s">
         <v>19</v>
       </c>
       <c r="L15">
-        <v>4.1913888888888903E-3</v>
+        <v>2.8125714285714299E-2</v>
       </c>
       <c r="M15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -1108,7 +1065,7 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -1138,10 +1095,10 @@
         <v>19</v>
       </c>
       <c r="L16">
-        <v>7.1664285714285701E-3</v>
+        <v>1.25185714285714E-2</v>
       </c>
       <c r="M16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -1149,7 +1106,7 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -1170,19 +1127,19 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J17">
-        <v>2.7100000000000002E-3</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="K17" t="s">
         <v>19</v>
       </c>
       <c r="L17">
-        <v>5.4894871794871798E-3</v>
+        <v>3.9043902439024399E-2</v>
       </c>
       <c r="M17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -1190,7 +1147,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
@@ -1220,10 +1177,10 @@
         <v>19</v>
       </c>
       <c r="L18">
-        <v>1.16393333333333E-2</v>
+        <v>1.9061249999999998E-2</v>
       </c>
       <c r="M18" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -1231,7 +1188,7 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
@@ -1252,19 +1209,19 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J19">
-        <v>4.2700000000000002E-4</v>
+        <v>3.5400000000000002E-3</v>
       </c>
       <c r="K19" t="s">
         <v>19</v>
       </c>
       <c r="L19">
-        <v>1.27862962962963E-3</v>
+        <v>1.20622222222222E-2</v>
       </c>
       <c r="M19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -1272,7 +1229,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
@@ -1302,7 +1259,7 @@
         <v>19</v>
       </c>
       <c r="L20">
-        <v>0.20218644067796601</v>
+        <v>0.23545762711864399</v>
       </c>
       <c r="M20" t="s">
         <v>20</v>
@@ -1313,7 +1270,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
@@ -1337,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>1.8100000000000001E-4</v>
+        <v>1.8200000000000001E-4</v>
       </c>
       <c r="K21" t="s">
         <v>19</v>
       </c>
       <c r="L21">
-        <v>6.8090476190476202E-4</v>
+        <v>9.8494117647058795E-4</v>
       </c>
       <c r="M21" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1355,6 +1312,5 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>